--- a/results/two_models_v2/experimental_results.XLSX
+++ b/results/two_models_v2/experimental_results.XLSX
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="131">
   <si>
     <t>Scheduler</t>
   </si>
@@ -391,6 +391,27 @@
   </si>
   <si>
     <t>UF_LabelSmooth</t>
+  </si>
+  <si>
+    <t>class_aware</t>
+  </si>
+  <si>
+    <t>DS_ClassAug</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>DS_StdAll</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>UF_ClassAug</t>
+  </si>
+  <si>
+    <t>UF_StdAll</t>
   </si>
 </sst>
 </file>
@@ -730,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
@@ -1421,6 +1442,106 @@
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
     </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42">
+        <v>0.26050000000000001</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42">
+        <v>-8.8099999999999998E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43">
+        <v>0.34860000000000002</v>
+      </c>
+      <c r="E43">
+        <v>6</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" t="s">
+        <v>126</v>
+      </c>
+      <c r="D44">
+        <v>0.23710000000000001</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>-7.1199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" t="s">
+        <v>128</v>
+      </c>
+      <c r="D45">
+        <v>0.30830000000000002</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
